--- a/artfynd/A 42261-2025 artfynd.xlsx
+++ b/artfynd/A 42261-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4955737</v>
+        <v>1340866</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605042.9606083664</v>
+        <v>605043</v>
       </c>
       <c r="R2" t="n">
-        <v>6718031.321467029</v>
+        <v>6718031</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2011-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1340866</v>
+        <v>4955736</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605042.9606083664</v>
+        <v>604900</v>
       </c>
       <c r="R3" t="n">
-        <v>6718031.321467029</v>
+        <v>6718247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2011-10-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4955736</v>
+        <v>4955737</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604900.2525452547</v>
+        <v>605043</v>
       </c>
       <c r="R4" t="n">
-        <v>6718247.424984375</v>
+        <v>6718031</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2011-10-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-10-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +969,7 @@
         <v>4955738</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604810.7366216887</v>
+        <v>604811</v>
       </c>
       <c r="R5" t="n">
-        <v>6718294.474509522</v>
+        <v>6718294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2011-10-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-10-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 42261-2025 artfynd.xlsx
+++ b/artfynd/A 42261-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1340866</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4955736</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4955737</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4955738</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>